--- a/data/trans_camb/IP09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 28,79</t>
+          <t>-28,6; 32,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 51,37</t>
+          <t>-13,49; 56,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 32,08</t>
+          <t>-31,92; 35,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 22,34</t>
+          <t>-24,81; 22,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 21,12</t>
+          <t>-32,77; 20,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,33; 4,69</t>
+          <t>-42,76; 6,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 18,95</t>
+          <t>-17,8; 18,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 28,02</t>
+          <t>-14,13; 27,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 8,51</t>
+          <t>-31,55; 9,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 339,51</t>
+          <t>-54,75; 430,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,68; 421,81</t>
+          <t>-35,27; 647,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 337,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 152,9</t>
+          <t>-57,27; 162,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 130,44</t>
+          <t>-79,66; 123,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,98</t>
+          <t>-100,0; 115,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 104,92</t>
+          <t>-43,15; 100,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 142,82</t>
+          <t>-38,09; 137,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-85,45; 54,59</t>
+          <t>-81,6; 60,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 32,49</t>
+          <t>-4,3; 33,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 40,62</t>
+          <t>-3,95; 38,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 62,65</t>
+          <t>6,13; 61,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 20,89</t>
+          <t>-12,42; 21,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 53,51</t>
+          <t>12,61; 55,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 35,94</t>
+          <t>-3,39; 34,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 21,46</t>
+          <t>-2,2; 22,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 41,79</t>
+          <t>12,52; 40,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 38,53</t>
+          <t>5,06; 38,2</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 439,46</t>
+          <t>-22,54; 446,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 614,54</t>
+          <t>-22,01; 583,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 803,0</t>
+          <t>17,94; 813,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,75; 151,79</t>
+          <t>-45,03; 165,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,23; 427,72</t>
+          <t>43,34; 441,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 268,32</t>
+          <t>-13,72; 247,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 179,48</t>
+          <t>-13,73; 161,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,04; 336,39</t>
+          <t>47,31; 323,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,19; 301,18</t>
+          <t>17,2; 276,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 35,53</t>
+          <t>-15,91; 34,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 50,86</t>
+          <t>-21,56; 47,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 49,55</t>
+          <t>-10,6; 49,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 14,61</t>
+          <t>-42,93; 11,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 64,41</t>
+          <t>-13,67; 62,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 29,75</t>
+          <t>-29,86; 28,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 17,48</t>
+          <t>-22,44; 17,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 45,17</t>
+          <t>-6,82; 48,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 30,26</t>
+          <t>-10,64; 29,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,57; 375,35</t>
+          <t>-45,72; 350,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 438,31</t>
+          <t>-62,06; 382,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 494,76</t>
+          <t>-29,0; 484,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,1; 66,07</t>
+          <t>-80,26; 45,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 270,98</t>
+          <t>-21,92; 257,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,81; 126,11</t>
+          <t>-52,66; 127,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 83,58</t>
+          <t>-53,82; 76,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 183,85</t>
+          <t>-16,27; 205,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 143,74</t>
+          <t>-24,3; 131,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 40,54</t>
+          <t>-26,77; 41,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,39; 49,06</t>
+          <t>-25,77; 50,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 43,7</t>
+          <t>-31,96; 39,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 41,88</t>
+          <t>-5,34; 45,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 36,26</t>
+          <t>-23,31; 33,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,88; 13,21</t>
+          <t>-33,77; 16,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 37,79</t>
+          <t>-2,1; 36,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 31,93</t>
+          <t>-12,71; 30,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 16,47</t>
+          <t>-23,29; 18,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 381,1</t>
+          <t>-50,09; 454,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 463,96</t>
+          <t>-56,21; 472,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 569,39</t>
+          <t>-77,73; 721,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 194,13</t>
+          <t>-12,22; 256,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 189,1</t>
+          <t>-57,52; 153,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-73,9; 51,71</t>
+          <t>-75,07; 71,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 188,45</t>
+          <t>-5,01; 177,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 138,25</t>
+          <t>-34,15; 149,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 72,44</t>
+          <t>-57,9; 94,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 24,55</t>
+          <t>-0,71; 23,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 30,69</t>
+          <t>3,92; 31,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 33,59</t>
+          <t>1,71; 36,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 15,9</t>
+          <t>-6,24; 15,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 30,91</t>
+          <t>4,58; 30,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 13,15</t>
+          <t>-12,25; 12,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 16,68</t>
+          <t>-1,39; 15,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7,24; 28,02</t>
+          <t>6,05; 26,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 18,29</t>
+          <t>-3,49; 17,74</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 162,37</t>
+          <t>-3,05; 147,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,12; 191,37</t>
+          <t>10,14; 185,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 199,92</t>
+          <t>2,11; 214,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 67,06</t>
+          <t>-17,27; 68,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,96; 132,31</t>
+          <t>12,38; 127,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 55,18</t>
+          <t>-36,24; 52,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 79,17</t>
+          <t>-4,63; 70,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>22,02; 125,12</t>
+          <t>20,67; 120,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 83,37</t>
+          <t>-11,99; 76,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,6; 32,63</t>
+          <t>-27,97; 30,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 56,75</t>
+          <t>-19,61; 53,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 35,78</t>
+          <t>-34,2; 35,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 22,78</t>
+          <t>-25,34; 22,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 20,83</t>
+          <t>-33,5; 20,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 6,77</t>
+          <t>-42,39; 5,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 18,9</t>
+          <t>-18,5; 18,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 27,73</t>
+          <t>-15,99; 26,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 9,19</t>
+          <t>-32,92; 6,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 430,78</t>
+          <t>-57,94; 333,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 647,21</t>
+          <t>-45,31; 558,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,13; 396,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,27; 162,49</t>
+          <t>-57,62; 151,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,66; 123,99</t>
+          <t>-79,87; 139,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,91</t>
+          <t>-100,0; 113,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,15; 100,31</t>
+          <t>-43,23; 102,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 137,92</t>
+          <t>-44,04; 138,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,6; 60,72</t>
+          <t>-83,37; 49,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 33,79</t>
+          <t>-3,29; 34,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 38,06</t>
+          <t>-2,8; 39,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 61,92</t>
+          <t>7,88; 62,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 21,93</t>
+          <t>-11,23; 21,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,61; 55,45</t>
+          <t>12,59; 53,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 34,33</t>
+          <t>-4,32; 33,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 22,59</t>
+          <t>-3,96; 20,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,52; 40,5</t>
+          <t>11,96; 41,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 38,2</t>
+          <t>6,8; 37,23</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 446,99</t>
+          <t>-17,3; 503,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 583,35</t>
+          <t>-23,72; 531,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,94; 813,41</t>
+          <t>25,16; 880,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 165,78</t>
+          <t>-40,99; 179,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,34; 441,76</t>
+          <t>40,37; 406,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 247,35</t>
+          <t>-17,22; 243,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 161,96</t>
+          <t>-16,49; 160,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47,31; 323,63</t>
+          <t>44,89; 308,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,2; 276,43</t>
+          <t>27,0; 284,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 34,88</t>
+          <t>-17,7; 33,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 47,41</t>
+          <t>-16,71; 51,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 49,1</t>
+          <t>-8,63; 48,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 11,2</t>
+          <t>-41,33; 12,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 62,47</t>
+          <t>-6,76; 65,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,86; 28,78</t>
+          <t>-27,18; 29,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 17,4</t>
+          <t>-21,15; 18,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 48,44</t>
+          <t>-6,77; 47,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 29,33</t>
+          <t>-9,72; 32,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,72; 350,68</t>
+          <t>-43,23; 323,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 382,65</t>
+          <t>-61,75; 427,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,0; 484,15</t>
+          <t>-24,61; 457,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,26; 45,86</t>
+          <t>-79,48; 58,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 257,91</t>
+          <t>-5,69; 263,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 127,59</t>
+          <t>-51,13; 127,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,82; 76,83</t>
+          <t>-50,25; 84,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 205,08</t>
+          <t>-13,75; 192,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 131,94</t>
+          <t>-23,49; 143,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 41,98</t>
+          <t>-23,26; 42,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 50,52</t>
+          <t>-26,09; 47,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 39,75</t>
+          <t>-32,47; 40,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 45,12</t>
+          <t>-4,77; 44,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 33,92</t>
+          <t>-24,23; 35,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,77; 16,51</t>
+          <t>-35,89; 16,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 36,02</t>
+          <t>-3,04; 34,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 30,04</t>
+          <t>-15,21; 30,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 18,05</t>
+          <t>-25,57; 16,49</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 454,92</t>
+          <t>-47,63; 426,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,21; 472,6</t>
+          <t>-51,33; 463,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,73; 721,71</t>
+          <t>-74,52; 523,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 256,17</t>
+          <t>-9,74; 260,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,52; 153,09</t>
+          <t>-61,96; 161,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 71,14</t>
+          <t>-74,28; 76,64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 177,4</t>
+          <t>-8,38; 165,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 149,25</t>
+          <t>-40,01; 137,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,9; 94,97</t>
+          <t>-59,79; 74,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 23,39</t>
+          <t>-0,74; 23,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 31,46</t>
+          <t>3,13; 33,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 36,06</t>
+          <t>1,73; 37,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 15,23</t>
+          <t>-6,33; 16,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,58; 30,36</t>
+          <t>3,73; 31,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 12,94</t>
+          <t>-11,9; 13,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 15,4</t>
+          <t>-0,83; 15,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,05; 26,69</t>
+          <t>8,1; 28,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 17,74</t>
+          <t>-3,14; 17,86</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 147,02</t>
+          <t>-4,51; 144,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10,14; 185,73</t>
+          <t>8,77; 204,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2,11; 214,68</t>
+          <t>1,81; 222,99</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 68,12</t>
+          <t>-18,19; 71,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,38; 127,46</t>
+          <t>12,24; 137,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 52,1</t>
+          <t>-36,6; 56,23</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 70,76</t>
+          <t>-3,04; 70,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,67; 120,79</t>
+          <t>26,08; 133,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 76,84</t>
+          <t>-10,86; 77,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP09-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP09-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,82</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-20,59</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>20,66</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,82</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,82</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-20,6</t>
+          <t>-2,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-13,22</t>
+          <t>-12,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-27,97; 30,7</t>
+          <t>-25,5; 22,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,61; 53,49</t>
+          <t>-34,01; 21,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 35,85</t>
+          <t>-42,32; 5,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 22,33</t>
+          <t>-27,51; 28,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 20,85</t>
+          <t>-14,22; 51,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 5,71</t>
+          <t>-36,47; 30,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 18,36</t>
+          <t>-16,67; 18,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 26,9</t>
+          <t>-15,23; 28,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 6,66</t>
+          <t>-30,8; 8,48</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-0,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-19,67%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-69,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>70,1%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,16%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-19,67%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-69,63%</t>
+          <t>-6,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-44,76%</t>
+          <t>-42,91%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 333,13</t>
+          <t>-60,17; 152,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-45,31; 558,2</t>
+          <t>-79,28; 130,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,13; 396,09</t>
+          <t>-100,0; 111,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,62; 151,15</t>
+          <t>-57,37; 339,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,87; 139,04</t>
+          <t>-39,68; 421,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,55</t>
+          <t>-83,11; 321,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 102,52</t>
+          <t>-41,32; 104,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 138,01</t>
+          <t>-40,77; 142,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,37; 49,47</t>
+          <t>-83,97; 56,66</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34,51</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,88</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>15,68</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17,47</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35,61</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,36</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,51</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,47</t>
+          <t>35,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21,94</t>
+          <t>22,71</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 34,32</t>
+          <t>-12,4; 20,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 39,78</t>
+          <t>12,86; 53,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 62,34</t>
+          <t>-4,51; 35,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 21,98</t>
+          <t>-3,76; 32,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 53,1</t>
+          <t>-4,06; 40,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 33,36</t>
+          <t>7,58; 62,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 20,71</t>
+          <t>-3,33; 21,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 41,34</t>
+          <t>10,07; 41,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 37,23</t>
+          <t>6,14; 39,28</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,72%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>163,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75,41%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>98,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>109,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>222,64%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>163,89%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>223,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115,67%</t>
+          <t>119,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 503,3</t>
+          <t>-45,75; 151,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 531,31</t>
+          <t>44,23; 427,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,16; 880,17</t>
+          <t>-17,86; 268,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,99; 179,32</t>
+          <t>-18,1; 439,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>40,37; 406,05</t>
+          <t>-23,61; 614,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 243,6</t>
+          <t>15,85; 809,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 160,07</t>
+          <t>-14,07; 179,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,89; 308,36</t>
+          <t>38,04; 336,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,0; 284,25</t>
+          <t>23,13; 307,21</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-15,65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35,55</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>9,7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>14,81</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>21,08</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-15,65</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,55</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>21,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,28</t>
+          <t>11,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 33,37</t>
+          <t>-41,01; 14,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 51,59</t>
+          <t>-5,98; 64,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 48,12</t>
+          <t>-24,46; 31,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 12,27</t>
+          <t>-17,13; 35,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 65,09</t>
+          <t>-20,33; 50,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 29,71</t>
+          <t>-6,16; 49,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 18,2</t>
+          <t>-21,98; 17,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 47,08</t>
+          <t>-5,16; 45,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 32,03</t>
+          <t>-8,89; 32,18</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-38,26%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86,91%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>38,79%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>59,19%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>84,27%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-38,26%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>86,91%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 323,72</t>
+          <t>-80,1; 66,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,75; 427,47</t>
+          <t>-5,07; 270,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 457,68</t>
+          <t>-45,28; 134,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,48; 58,71</t>
+          <t>-44,57; 375,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 263,65</t>
+          <t>-60,17; 438,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,13; 127,19</t>
+          <t>-20,87; 487,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 84,83</t>
+          <t>-50,59; 83,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 192,99</t>
+          <t>-13,49; 183,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 143,25</t>
+          <t>-21,35; 147,02</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22,27</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,71</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9,5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12,98</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,89</t>
+          <t>-12,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,66</t>
+          <t>-9,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 42,35</t>
+          <t>-4,44; 41,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 47,1</t>
+          <t>-26,43; 36,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 40,8</t>
+          <t>-32,19; 13,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 44,79</t>
+          <t>-24,32; 40,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 35,41</t>
+          <t>-25,39; 49,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,89; 16,77</t>
+          <t>-44,19; 13,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 34,58</t>
+          <t>-1,48; 37,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 30,04</t>
+          <t>-15,22; 31,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 16,49</t>
+          <t>-28,81; 6,56</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>67,11%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-20,21%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>30,18%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>41,22%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>67,11%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-23,77%</t>
+          <t>-40,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,26%</t>
+          <t>-28,33%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 426,85</t>
+          <t>-10,53; 194,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 463,29</t>
+          <t>-57,91; 189,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,52; 523,5</t>
+          <t>-70,28; 57,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 260,7</t>
+          <t>-49,84; 381,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 161,56</t>
+          <t>-55,41; 463,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 76,64</t>
+          <t>-84,76; 133,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 165,36</t>
+          <t>-5,14; 188,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 137,03</t>
+          <t>-39,02; 138,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,79; 74,95</t>
+          <t>-65,83; 32,68</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,64</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>17,41</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>11,51</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>17,72</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,31</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>10,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>5,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 23,05</t>
+          <t>-6,7; 15,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 33,18</t>
+          <t>2,46; 30,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,73; 37,29</t>
+          <t>-11,24; 14,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 16,13</t>
+          <t>-0,73; 24,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,73; 31,16</t>
+          <t>2,15; 30,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 13,14</t>
+          <t>-3,26; 23,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 15,45</t>
+          <t>-0,29; 16,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,1; 28,92</t>
+          <t>7,24; 28,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 17,86</t>
+          <t>-3,32; 15,17</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>60,46%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>50,56%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>77,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>16,12%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>60,46%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 144,58</t>
+          <t>-18,99; 67,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8,77; 204,64</t>
+          <t>6,96; 132,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1,81; 222,99</t>
+          <t>-34,38; 59,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 71,91</t>
+          <t>-3,38; 162,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>12,24; 137,67</t>
+          <t>8,12; 191,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 56,23</t>
+          <t>-12,54; 153,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 70,84</t>
+          <t>-1,4; 79,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,08; 133,99</t>
+          <t>22,02; 125,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 77,03</t>
+          <t>-11,43; 67,79</t>
         </is>
       </c>
     </row>
